--- a/data/trans_bre/P23_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P23_R-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,41; -17,58</t>
+          <t>-27,61; -17,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,92; -9,45</t>
+          <t>-20,16; -10,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -6,25</t>
+          <t>-16,37; -6,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-56,76; -40,65</t>
+          <t>-56,79; -40,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,53; -27,36</t>
+          <t>-49,18; -28,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,69; -18,41</t>
+          <t>-41,71; -19,66</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,09; -14,63</t>
+          <t>-23,25; -14,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,99; -7,7</t>
+          <t>-15,85; -7,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,44; -3,27</t>
+          <t>-11,2; -3,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,95; -36,32</t>
+          <t>-51,66; -35,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,98; -20,11</t>
+          <t>-38,26; -19,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,16; -9,45</t>
+          <t>-31,78; -10,06</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -7,29</t>
+          <t>-17,44; -7,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,76; -6,38</t>
+          <t>-16,54; -6,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,42; -7,04</t>
+          <t>-17,09; -7,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-43,92; -20,93</t>
+          <t>-43,34; -21,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,22; -17,01</t>
+          <t>-38,09; -16,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,87; -18,4</t>
+          <t>-39,25; -18,74</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -9,51</t>
+          <t>-17,7; -9,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -5,57</t>
+          <t>-14,9; -6,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,05; -1,35</t>
+          <t>-10,15; -2,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,12; -23,02</t>
+          <t>-39,47; -23,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,74; -16,02</t>
+          <t>-35,97; -16,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,14; -4,7</t>
+          <t>-31,18; -7,45</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -14,32</t>
+          <t>-19,08; -14,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -9,69</t>
+          <t>-14,42; -9,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -6,66</t>
+          <t>-11,2; -6,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -34,82</t>
+          <t>-43,64; -35,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,21; -25,25</t>
+          <t>-35,28; -25,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -19,66</t>
+          <t>-30,72; -19,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P23_R-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,61; -17,72</t>
+          <t>-27,35; -17,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,16; -10,08</t>
+          <t>-19,7; -10,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -6,89</t>
+          <t>-16,99; -7,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-56,79; -40,15</t>
+          <t>-56,46; -40,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,18; -28,13</t>
+          <t>-49,07; -28,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,71; -19,66</t>
+          <t>-42,65; -20,87</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,25; -14,64</t>
+          <t>-23,28; -14,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,85; -7,3</t>
+          <t>-16,33; -7,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -3,06</t>
+          <t>-11,38; -2,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,66; -35,94</t>
+          <t>-52,02; -36,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,26; -19,63</t>
+          <t>-38,3; -19,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,78; -10,06</t>
+          <t>-31,89; -9,34</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,44; -7,62</t>
+          <t>-17,6; -7,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,54; -6,41</t>
+          <t>-17,08; -6,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,09; -7,3</t>
+          <t>-17,2; -7,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-43,34; -21,76</t>
+          <t>-43,44; -20,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,09; -16,92</t>
+          <t>-38,32; -17,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,25; -18,74</t>
+          <t>-40,09; -19,34</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,7; -9,57</t>
+          <t>-18,03; -9,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,9; -6,11</t>
+          <t>-15,06; -6,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -2,18</t>
+          <t>-9,94; -2,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,47; -23,34</t>
+          <t>-39,93; -23,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,97; -16,72</t>
+          <t>-36,64; -17,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,18; -7,45</t>
+          <t>-30,75; -7,92</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -14,65</t>
+          <t>-18,96; -14,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -9,74</t>
+          <t>-14,4; -9,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -6,65</t>
+          <t>-11,33; -6,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -35,66</t>
+          <t>-43,67; -35,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,28; -25,5</t>
+          <t>-35,29; -25,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,72; -19,76</t>
+          <t>-31,15; -19,86</t>
         </is>
       </c>
     </row>
